--- a/tests/workbooktests/workbooks/test_volatilities.xlsx
+++ b/tests/workbooktests/workbooks/test_volatilities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32278BA2-0667-4C70-8349-A9D816851C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316FEEB2-3ADE-471A-81E3-E0A7ED95AB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{03D12B07-F690-4065-A8E3-371E349FECFA}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" activeTab="2" xr2:uid="{03D12B07-F690-4065-A8E3-371E349FECFA}"/>
   </bookViews>
   <sheets>
     <sheet name="qlBlackConstantVol" sheetId="1" r:id="rId1"/>
@@ -325,7 +325,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -378,10 +378,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,27 +760,27 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="str" cm="1">
-        <f t="array" ref="B6">_xll.qlBlackConstantVol(B1,B2,B3,B4)</f>
-        <v>欣[test_volatilities.xlsx]qlBlackConstantVol!R6C2BlackVolTermStructureHandle,A</v>
+      <c r="B6" t="e" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">_xll.qlBlackConstantVol(B1,B2,B3,B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" cm="1">
-        <f t="array" ref="B8">_xll.qlBlackVolTermStructureMinStrike(B6)</f>
-        <v>-1.7976931348623157E+308</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlBlackVolTermStructureMinStrike(B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" cm="1">
-        <f t="array" ref="B9">_xll.qlBlackVolTermStructureMaxStrike(B6)</f>
-        <v>1.7976931348623157E+308</v>
+      <c r="B9" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlBlackVolTermStructureMaxStrike(B6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -796,9 +796,9 @@
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" cm="1">
-        <f t="array" ref="B12">_xll.qlTermStructureTimeFromReference(B6,B11)</f>
-        <v>1</v>
+      <c r="B12" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlTermStructureTimeFromReference(B6,B11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -822,9 +822,9 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2" cm="1">
-        <f t="array" ref="B16">_xll.qlTermStructureTimeFromReference(B6,B15)</f>
-        <v>2</v>
+      <c r="B16" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlTermStructureTimeFromReference(B6,B15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -834,27 +834,27 @@
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" cm="1">
-        <f t="array" ref="B18">_xll.qlBlackVolTermStructureBlackVol(B6,B11,B13)</f>
-        <v>0.25</v>
+      <c r="B18" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlBlackVolTermStructureBlackVol(B6,B11,B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" cm="1">
-        <f t="array" ref="B19">_xll.qlBlackVolTermStructureBlackVolFromTime(B6,B12,B13)</f>
-        <v>0.25</v>
+      <c r="B19" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlBlackVolTermStructureBlackVolFromTime(B6,B12,B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="B21" cm="1">
-        <f t="array" ref="B21">_xll.qlBlackVolTermStructureBlackVariance(B6,B15,B13)</f>
-        <v>0.125</v>
+      <c r="B21" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlBlackVolTermStructureBlackVariance(B6,B15,B13)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -864,49 +864,49 @@
       <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" cm="1">
-        <f t="array" ref="B22">_xll.qlBlackVolTermStructureBlackVarianceFromTime(B6,B16,B13)</f>
-        <v>0.125</v>
-      </c>
-      <c r="D22">
-        <f>B3*B3*B16</f>
-        <v>0.125</v>
+      <c r="B22" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackVolTermStructureBlackVarianceFromTime(B6,B16,B13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D22" t="e">
+        <f ca="1">B3*B3*B16</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
-      <c r="B24" cm="1">
-        <f t="array" ref="B24">_xll.qlBlackVolTermStructureBlackForwardVol(B6,B11,B15,B13)</f>
-        <v>0.25</v>
+      <c r="B24" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBlackVolTermStructureBlackForwardVol(B6,B11,B15,B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B25" cm="1">
-        <f t="array" ref="B25">_xll.qlBlackVolTermStructureBlackForwardVolFromTime(B6,B12,B16,B13)</f>
-        <v>0.25</v>
+      <c r="B25" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlBlackVolTermStructureBlackForwardVolFromTime(B6,B12,B16,B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" cm="1">
-        <f t="array" ref="B27">_xll.qlBlackVolTermStructureBlackForwardVariance(B6,B11,B15,B13)</f>
-        <v>6.25E-2</v>
+      <c r="B27" t="e" cm="1">
+        <f t="array" aca="1" ref="B27" ca="1">_xll.qlBlackVolTermStructureBlackForwardVariance(B6,B11,B15,B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="B28" cm="1">
-        <f t="array" ref="B28">_xll.qlBlackVolTermStructureBlackForwardVarianceFromTime(B6,B12,B16,B13)</f>
-        <v>6.25E-2</v>
+      <c r="B28" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlBlackVolTermStructureBlackForwardVarianceFromTime(B6,B12,B16,B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1020,13 +1020,13 @@
       <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlConstantOptionletVolatility(B1,B2,B3,B4,B5)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantOptionletVolatility!R8C2OptionletVolatilityStructureHandle,A</v>
-      </c>
-      <c r="C8" s="3" t="str" cm="1">
-        <f t="array" ref="C8">_xll.qlConstantOptionletVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantOptionletVolatility!R8C3OptionletVolatilityStructureHandle,A</v>
+      <c r="B8" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlConstantOptionletVolatility(B1,B2,B3,B4,B5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_xll.qlConstantOptionletVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1046,13 +1046,13 @@
       <c r="A11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="9" cm="1">
-        <f t="array" ref="B11">_xll.qlTermStructureTimeFromReference(B8,B10)</f>
-        <v>1</v>
-      </c>
-      <c r="C11" s="9" cm="1">
-        <f t="array" ref="C11">_xll.qlTermStructureTimeFromReference(C8,C10)</f>
-        <v>1</v>
+      <c r="B11" s="9" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlTermStructureTimeFromReference(B8,B10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="9" t="e" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">_xll.qlTermStructureTimeFromReference(C8,C10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1078,52 +1078,52 @@
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" cm="1">
-        <f t="array" ref="B15">_xll.qlOptionletVolatilityStructureVolatility(B8,B10,B12)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C15" s="7" cm="1">
-        <f t="array" ref="C15">_xll.qlOptionletVolatilityStructureVolatility(C8,C10,C12,C13)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B15" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlOptionletVolatilityStructureVolatility(B8,B10,B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlOptionletVolatilityStructureVolatility(C8,C10,C12,C13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" cm="1">
-        <f t="array" ref="B16">_xll.qlOptionletVolatilityStructureVolatilityFromTime(B8,B11,B12)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C16" s="7" cm="1">
-        <f t="array" ref="C16">_xll.qlOptionletVolatilityStructureVolatilityFromTime(C8,C11,C12,C13)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B16" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlOptionletVolatilityStructureVolatilityFromTime(B8,B11,B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C16" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">_xll.qlOptionletVolatilityStructureVolatilityFromTime(C8,C11,C12,C13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="7" cm="1">
-        <f t="array" ref="B17">_xll.qlOptionletVolatilityStructureBlackVariance(B8,B10,B12)</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="C17" s="10" cm="1">
-        <f t="array" ref="C17">_xll.qlOptionletVolatilityStructureBlackVariance(C8,C10,C12,C13)</f>
-        <v>6.3999999999999997E-5</v>
+      <c r="B17" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlOptionletVolatilityStructureBlackVariance(B8,B10,B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" s="10" t="e" cm="1">
+        <f t="array" aca="1" ref="C17" ca="1">_xll.qlOptionletVolatilityStructureBlackVariance(C8,C10,C12,C13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="7" cm="1">
-        <f t="array" ref="B18">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(B8,B11,B12)</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="C18" s="10" cm="1">
-        <f t="array" ref="C18">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(C8,C11,C12,C13)</f>
-        <v>6.3999999999999997E-5</v>
+      <c r="B18" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(B8,B11,B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" s="10" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(C8,C11,C12,C13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1215,13 +1215,13 @@
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="3" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlConstantSwaptionVolatility(B1,B2,B3,B4,B5)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R8C2SwaptionVolatilityStructureHandle,A</v>
-      </c>
-      <c r="C8" s="3" t="str" cm="1">
-        <f t="array" ref="C8">_xll.qlConstantSwaptionVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R8C3SwaptionVolatilityStructureHandle,A</v>
+      <c r="B8" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlConstantSwaptionVolatility(B1,B2,B3,B4,B5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_xll.qlConstantSwaptionVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1242,26 +1242,26 @@
       <c r="A11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="4" cm="1">
-        <f t="array" ref="B11">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(B8,B10)</f>
-        <v>46539</v>
-      </c>
-      <c r="C11" s="4" cm="1">
-        <f t="array" ref="C11">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(C8,C10)</f>
-        <v>46539</v>
+      <c r="B11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(B8,B10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(C8,C10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="9" cm="1">
-        <f t="array" ref="B12">_xll.qlTermStructureTimeFromReference(B8,B11)</f>
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" cm="1">
-        <f t="array" ref="C12">_xll.qlTermStructureTimeFromReference(C8,C11)</f>
-        <v>1</v>
+      <c r="B12" s="9" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlTermStructureTimeFromReference(B8,B11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="9" t="e" cm="1">
+        <f t="array" aca="1" ref="C12" ca="1">_xll.qlTermStructureTimeFromReference(C8,C11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1309,122 +1309,104 @@
       <c r="A18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="6" cm="1">
-        <f t="array" ref="B18">_xll.qlSwaptionVolatilityStructureVolatility(B8,B11,B13,B15)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C18" s="7" cm="1">
-        <f t="array" ref="C18">_xll.qlSwaptionVolatilityStructureVolatility(C8,C11,C13,C15,C16)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B18" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlSwaptionVolatilityStructureVolatility(B8,B11,B13,B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlSwaptionVolatilityStructureVolatility(C8,C11,C13,C15,C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="6" cm="1">
-        <f t="array" ref="B19">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(B8,B12,B14,B15)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C19" s="7" cm="1">
-        <f t="array" ref="C19">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(C8,C12,C14,C15,C16)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B19" s="6" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(B8,B12,B14,B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="C19" ca="1">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(C8,C12,C14,C15,C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="7" cm="1">
-        <f t="array" ref="B20">_xll.qlSwaptionVolatilityStructureBlackVariance(B8,B11,B13,B15)</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="C20" s="10" cm="1">
-        <f t="array" ref="C20">_xll.qlSwaptionVolatilityStructureBlackVariance(C8,C11,C13,C15,C16)</f>
-        <v>6.3999999999999997E-5</v>
+      <c r="B20" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlSwaptionVolatilityStructureBlackVariance(B8,B11,B13,B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C20" s="10" t="e" cm="1">
+        <f t="array" aca="1" ref="C20" ca="1">_xll.qlSwaptionVolatilityStructureBlackVariance(C8,C11,C13,C15,C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="7" cm="1">
-        <f t="array" ref="B21">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(B8,B12,B14,B15)</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="C21" s="10" cm="1">
-        <f t="array" ref="C21">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(C8,C12,C14,C15)</f>
-        <v>6.3999999999999997E-5</v>
+      <c r="B21" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(B8,B12,B14,B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C21" s="10" t="e" cm="1">
+        <f t="array" aca="1" ref="C21" ca="1">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(C8,C12,C14,C15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="7" cm="1">
-        <f t="array" ref="B22">_xll.qlSwaptionVolatilityStructureShift(B8,B11,B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="11" t="str" cm="1">
-        <f t="array" ref="C22">_xll.qlSwaptionVolatilityStructureShift(C8,C11,C13,C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\volatilities.py", line 760, in qlSwaptionVolatilityStructureShift
-    return vol_tsh.shift(option_date, swap_tenor, extrapolate)
-           ~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 12304, in shift
-    return _QuantLib.SwaptionVolatilityStructureHandle_shift(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: shift parameter only makes sense for lognormal volatilities
-</v>
+      <c r="B22" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlSwaptionVolatilityStructureShift(B8,B11,B13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C22" s="12" t="e" cm="1">
+        <f t="array" aca="1" ref="C22" ca="1">FIND("RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities",_xll.qlSwaptionVolatilityStructureShift(C8,C11,C13,C16))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="7" cm="1">
-        <f t="array" ref="B23">_xll.qlSwaptionVolatilityStructureShiftFromTime(B8,B12,B14)</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="11" t="str" cm="1">
-        <f t="array" ref="C23">_xll.qlSwaptionVolatilityStructureShiftFromTime(C8,C12,C14,C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\volatilities.py", line 781, in qlSwaptionVolatilityStructureShiftFromTime
-    return vol_tsh.shift(option_time, swap_length, extrapolate)
-           ~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 12304, in shift
-    return _QuantLib.SwaptionVolatilityStructureHandle_shift(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: shift parameter only makes sense for lognormal volatilities
-</v>
+      <c r="B23" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlSwaptionVolatilityStructureShiftFromTime(B8,B12,B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C23" s="12" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">FIND("RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities", _xll.qlSwaptionVolatilityStructureShiftFromTime(C8,C12,C14,C16))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="3" t="str" cm="1">
-        <f t="array" ref="B24">_xll.qlSwaptionVolatilityStructureSmileSection(B8,B11,B13)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R24C2SmileSection,A</v>
-      </c>
-      <c r="C24" s="3" t="str" cm="1">
-        <f t="array" ref="C24">_xll.qlSwaptionVolatilityStructureSmileSection(C8,C11,C13,C16)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R24C3SmileSection,A</v>
+      <c r="B24" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlSwaptionVolatilityStructureSmileSection(B8,B11,B13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C24" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlSwaptionVolatilityStructureSmileSection(C8,C11,C13,C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="3" t="str" cm="1">
-        <f t="array" ref="B25">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(B8,B12,B14)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R25C2SmileSection,A</v>
-      </c>
-      <c r="C25" s="3" t="str" cm="1">
-        <f t="array" ref="C25">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(C8,C12,C14,C16)</f>
-        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R25C3SmileSection,A</v>
+      <c r="B25" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(B8,B12,B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C25" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="C25" ca="1">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(C8,C12,C14,C16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1489,20 +1471,20 @@
       <c r="D3" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="1" cm="1">
-        <f t="array" ref="E3">_xll.qlCalendarAdvance2("Target",$B$1,D3,"Following")</f>
-        <v>46539</v>
-      </c>
-      <c r="F3" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G3" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H3" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="E3" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E3" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D3,"Following")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F3" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I3" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -1510,20 +1492,20 @@
       <c r="D4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="1" cm="1">
-        <f t="array" ref="E4">_xll.qlCalendarAdvance2("Target",$B$1,D4,"Following")</f>
-        <v>46905</v>
-      </c>
-      <c r="F4" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G4" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H4" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="E4" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E4" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D4,"Following")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F4" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G4" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H4" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I4" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -1531,27 +1513,27 @@
       <c r="A5" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="3" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlSwaptionVolatilityMatrix(B1,E3:E7,F2:I2,F3:I7,B2,,"Normal")</f>
-        <v>欣[test_volatilities.xlsx]qlSwaptionVolatilityMatrix!R5C2SwaptionVolatilityStructureHandle,G</v>
+      <c r="B5" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlSwaptionVolatilityMatrix(B1,E3:E7,F2:I2,F3:I7,B2,,"Normal")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D5" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="1" cm="1">
-        <f t="array" ref="E5">_xll.qlCalendarAdvance2("Target",$B$1,D5,"Following")</f>
-        <v>47270</v>
-      </c>
-      <c r="F5" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G5" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H5" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="E5" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E5" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D5,"Following")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G5" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I5" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -1559,20 +1541,20 @@
       <c r="D6" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="1" cm="1">
-        <f t="array" ref="E6">_xll.qlCalendarAdvance2("Target",$B$1,D6,"Following")</f>
-        <v>47637</v>
-      </c>
-      <c r="F6" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G6" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H6" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="E6" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E6" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D6,"Following")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G6" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H6" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I6" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
@@ -1580,27 +1562,27 @@
       <c r="A7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="12" cm="1">
-        <f t="array" ref="B7">_xll.qlSwaptionVolatilityStructureVolatility(B5,E4+180,"3y",0)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B7" s="11" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlSwaptionVolatilityStructureVolatility(B5,E4+180,"3y",0)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="1" cm="1">
-        <f t="array" ref="E7">_xll.qlCalendarAdvance2("Target",$B$1,D7,"Following")</f>
-        <v>48001</v>
-      </c>
-      <c r="F7" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G7" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H7" s="12">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="E7" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E7" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D7,"Following")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G7" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I7" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>

--- a/tests/workbooktests/workbooks/test_volatilities.xlsx
+++ b/tests/workbooktests/workbooks/test_volatilities.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316FEEB2-3ADE-471A-81E3-E0A7ED95AB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E732A2BE-9EB0-4965-AB58-34488662C1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" activeTab="2" xr2:uid="{03D12B07-F690-4065-A8E3-371E349FECFA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{03D12B07-F690-4065-A8E3-371E349FECFA}"/>
   </bookViews>
   <sheets>
     <sheet name="qlBlackConstantVol" sheetId="1" r:id="rId1"/>
-    <sheet name="qlConstantOptionletVolatility" sheetId="2" r:id="rId2"/>
-    <sheet name="qlConstantSwaptionVolatility" sheetId="3" r:id="rId3"/>
-    <sheet name="qlSwaptionVolatilityMatrix" sheetId="4" r:id="rId4"/>
+    <sheet name="qlBlackVarianceCurve" sheetId="5" r:id="rId2"/>
+    <sheet name="qlConstantOptionletVolatility" sheetId="2" r:id="rId3"/>
+    <sheet name="qlConstantSwaptionVolatility" sheetId="3" r:id="rId4"/>
+    <sheet name="qlSwaptionVolatilityMatrix" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="89">
   <si>
     <t>Reference date</t>
   </si>
@@ -289,6 +290,48 @@
   </si>
   <si>
     <t>volatility type</t>
+  </si>
+  <si>
+    <t>Reference date for the variance curve.</t>
+  </si>
+  <si>
+    <t>dates</t>
+  </si>
+  <si>
+    <t>Vector of dates for the variance curve.</t>
+  </si>
+  <si>
+    <t>volatilities</t>
+  </si>
+  <si>
+    <t>Vector of volatilities corresponding to the dates.</t>
+  </si>
+  <si>
+    <t>Day count convention for the variance curve.</t>
+  </si>
+  <si>
+    <t>force_monotone_variance</t>
+  </si>
+  <si>
+    <t>Whether to force monotone variance (default: True).</t>
+  </si>
+  <si>
+    <t>time_extrapolation_type</t>
+  </si>
+  <si>
+    <t>The time extrapolation type for the curve (default: FlatVolatility).</t>
+  </si>
+  <si>
+    <t>Dates</t>
+  </si>
+  <si>
+    <t>Volatilities</t>
+  </si>
+  <si>
+    <t>FlatVolatility</t>
+  </si>
+  <si>
+    <t>qlBlackVarianceCurve</t>
   </si>
 </sst>
 </file>
@@ -352,7 +395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -381,6 +424,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -760,27 +806,27 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="e" cm="1">
-        <f t="array" aca="1" ref="B6" ca="1">_xll.qlBlackConstantVol(B1,B2,B3,B4)</f>
-        <v>#VALUE!</v>
+      <c r="B6" t="str" cm="1">
+        <f t="array" ref="B6">_xll.qlBlackConstantVol(B1,B2,B3,B4)</f>
+        <v>欣[test_volatilities.xlsx]qlBlackConstantVol!R6C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlBlackVolTermStructureMinStrike(B6)</f>
-        <v>#VALUE!</v>
+      <c r="B8" cm="1">
+        <f t="array" ref="B8">_xll.qlBlackVolTermStructureMinStrike(B6)</f>
+        <v>-1.7976931348623157E+308</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlBlackVolTermStructureMaxStrike(B6)</f>
-        <v>#VALUE!</v>
+      <c r="B9" cm="1">
+        <f t="array" ref="B9">_xll.qlBlackVolTermStructureMaxStrike(B6)</f>
+        <v>1.7976931348623157E+308</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -796,9 +842,9 @@
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlTermStructureTimeFromReference(B6,B11)</f>
-        <v>#VALUE!</v>
+      <c r="B12" s="2" cm="1">
+        <f t="array" ref="B12">_xll.qlTermStructureTimeFromReference(B6,B11)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -822,9 +868,9 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlTermStructureTimeFromReference(B6,B15)</f>
-        <v>#VALUE!</v>
+      <c r="B16" s="2" cm="1">
+        <f t="array" ref="B16">_xll.qlTermStructureTimeFromReference(B6,B15)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -834,27 +880,27 @@
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlBlackVolTermStructureBlackVol(B6,B11,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B18" cm="1">
+        <f t="array" ref="B18">_xll.qlBlackVolTermStructureBlackVol(B6,B11,B13)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlBlackVolTermStructureBlackVolFromTime(B6,B12,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B19" cm="1">
+        <f t="array" ref="B19">_xll.qlBlackVolTermStructureBlackVolFromTime(B6,B12,B13)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlBlackVolTermStructureBlackVariance(B6,B15,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B21" cm="1">
+        <f t="array" ref="B21">_xll.qlBlackVolTermStructureBlackVariance(B6,B15,B13)</f>
+        <v>0.125</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -864,49 +910,49 @@
       <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackVolTermStructureBlackVarianceFromTime(B6,B16,B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D22" t="e">
-        <f ca="1">B3*B3*B16</f>
-        <v>#VALUE!</v>
+      <c r="B22" cm="1">
+        <f t="array" ref="B22">_xll.qlBlackVolTermStructureBlackVarianceFromTime(B6,B16,B13)</f>
+        <v>0.125</v>
+      </c>
+      <c r="D22">
+        <f>B3*B3*B16</f>
+        <v>0.125</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
-      <c r="B24" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBlackVolTermStructureBlackForwardVol(B6,B11,B15,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B24" cm="1">
+        <f t="array" ref="B24">_xll.qlBlackVolTermStructureBlackForwardVol(B6,B11,B15,B13)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B25" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.qlBlackVolTermStructureBlackForwardVolFromTime(B6,B12,B16,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B25" cm="1">
+        <f t="array" ref="B25">_xll.qlBlackVolTermStructureBlackForwardVolFromTime(B6,B12,B16,B13)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" t="e" cm="1">
-        <f t="array" aca="1" ref="B27" ca="1">_xll.qlBlackVolTermStructureBlackForwardVariance(B6,B11,B15,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B27" cm="1">
+        <f t="array" ref="B27">_xll.qlBlackVolTermStructureBlackForwardVariance(B6,B11,B15,B13)</f>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="B28" t="e" cm="1">
-        <f t="array" aca="1" ref="B28" ca="1">_xll.qlBlackVolTermStructureBlackForwardVarianceFromTime(B6,B12,B16,B13)</f>
-        <v>#VALUE!</v>
+      <c r="B28" cm="1">
+        <f t="array" ref="B28">_xll.qlBlackVolTermStructureBlackForwardVarianceFromTime(B6,B12,B16,B13)</f>
+        <v>6.25E-2</v>
       </c>
     </row>
   </sheetData>
@@ -915,6 +961,142 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C21830-66DA-4F7B-92BB-975D8F594380}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="62.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <f>B1+365</f>
+        <v>46539</v>
+      </c>
+      <c r="B4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f>A4+365</f>
+        <v>46904</v>
+      </c>
+      <c r="B5">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f>A5+365</f>
+        <v>47269</v>
+      </c>
+      <c r="B6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f>A6+365</f>
+        <v>47634</v>
+      </c>
+      <c r="B7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1">
+        <f>B1</f>
+        <v>46174</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="3" t="str" cm="1">
+        <f t="array" ref="B15">_xll.qlBlackVarianceCurve(B9,A4:A7,B4:B7,B12,B13,B14)</f>
+        <v>欣[test_volatilities.xlsx]qlBlackVarianceCurve!R15C2BlackVarianceCurve,A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E334E1-BB58-4274-97F9-2A66D842EB70}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1020,13 +1202,13 @@
       <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlConstantOptionletVolatility(B1,B2,B3,B4,B5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_xll.qlConstantOptionletVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
-        <v>#VALUE!</v>
+      <c r="B8" s="3" t="str" cm="1">
+        <f t="array" ref="B8">_xll.qlConstantOptionletVolatility(B1,B2,B3,B4,B5)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantOptionletVolatility!R8C2OptionletVolatilityStructureHandle,A</v>
+      </c>
+      <c r="C8" s="3" t="str" cm="1">
+        <f t="array" ref="C8">_xll.qlConstantOptionletVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantOptionletVolatility!R8C3OptionletVolatilityStructureHandle,A</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1046,13 +1228,13 @@
       <c r="A11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="9" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlTermStructureTimeFromReference(B8,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="9" t="e" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">_xll.qlTermStructureTimeFromReference(C8,C10)</f>
-        <v>#VALUE!</v>
+      <c r="B11" s="9" cm="1">
+        <f t="array" ref="B11">_xll.qlTermStructureTimeFromReference(B8,B10)</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" cm="1">
+        <f t="array" ref="C11">_xll.qlTermStructureTimeFromReference(C8,C10)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1078,52 +1260,52 @@
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlOptionletVolatilityStructureVolatility(B8,B10,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlOptionletVolatilityStructureVolatility(C8,C10,C12,C13)</f>
-        <v>#VALUE!</v>
+      <c r="B15" s="6" cm="1">
+        <f t="array" ref="B15">_xll.qlOptionletVolatilityStructureVolatility(B8,B10,B12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C15" s="7" cm="1">
+        <f t="array" ref="C15">_xll.qlOptionletVolatilityStructureVolatility(C8,C10,C12,C13)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlOptionletVolatilityStructureVolatilityFromTime(B8,B11,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="C16" ca="1">_xll.qlOptionletVolatilityStructureVolatilityFromTime(C8,C11,C12,C13)</f>
-        <v>#VALUE!</v>
+      <c r="B16" s="6" cm="1">
+        <f t="array" ref="B16">_xll.qlOptionletVolatilityStructureVolatilityFromTime(B8,B11,B12)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C16" s="7" cm="1">
+        <f t="array" ref="C16">_xll.qlOptionletVolatilityStructureVolatilityFromTime(C8,C11,C12,C13)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlOptionletVolatilityStructureBlackVariance(B8,B10,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="C17" ca="1">_xll.qlOptionletVolatilityStructureBlackVariance(C8,C10,C12,C13)</f>
-        <v>#VALUE!</v>
+      <c r="B17" s="7" cm="1">
+        <f t="array" ref="B17">_xll.qlOptionletVolatilityStructureBlackVariance(B8,B10,B12)</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="C17" s="10" cm="1">
+        <f t="array" ref="C17">_xll.qlOptionletVolatilityStructureBlackVariance(C8,C10,C12,C13)</f>
+        <v>6.3999999999999997E-5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(B8,B11,B12)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="C18" ca="1">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(C8,C11,C12,C13)</f>
-        <v>#VALUE!</v>
+      <c r="B18" s="7" cm="1">
+        <f t="array" ref="B18">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(B8,B11,B12)</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="C18" s="10" cm="1">
+        <f t="array" ref="C18">_xll.qlOptionletVolatilityStructureBlackVarianceFromTime(C8,C11,C12,C13)</f>
+        <v>6.3999999999999997E-5</v>
       </c>
     </row>
   </sheetData>
@@ -1131,7 +1313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F7DD04-F97D-41C9-B20D-15577F3B15F2}">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1215,13 +1397,13 @@
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlConstantSwaptionVolatility(B1,B2,B3,B4,B5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_xll.qlConstantSwaptionVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
-        <v>#VALUE!</v>
+      <c r="B8" s="3" t="str" cm="1">
+        <f t="array" ref="B8">_xll.qlConstantSwaptionVolatility(B1,B2,B3,B4,B5)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R8C2SwaptionVolatilityStructureHandle,A</v>
+      </c>
+      <c r="C8" s="3" t="str" cm="1">
+        <f t="array" ref="C8">_xll.qlConstantSwaptionVolatility(C1,C2,C3,C4,C5,C6,C7)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R8C3SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1242,26 +1424,26 @@
       <c r="A11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(B8,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(C8,C10)</f>
-        <v>#VALUE!</v>
+      <c r="B11" s="4" cm="1">
+        <f t="array" ref="B11">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(B8,B10)</f>
+        <v>46539</v>
+      </c>
+      <c r="C11" s="4" cm="1">
+        <f t="array" ref="C11">_xll.qlSwaptionVolatilityStructureOptionDateFromTenor(C8,C10)</f>
+        <v>46539</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="9" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlTermStructureTimeFromReference(B8,B11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="9" t="e" cm="1">
-        <f t="array" aca="1" ref="C12" ca="1">_xll.qlTermStructureTimeFromReference(C8,C11)</f>
-        <v>#VALUE!</v>
+      <c r="B12" s="9" cm="1">
+        <f t="array" ref="B12">_xll.qlTermStructureTimeFromReference(B8,B11)</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="9" cm="1">
+        <f t="array" ref="C12">_xll.qlTermStructureTimeFromReference(C8,C11)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1309,104 +1491,104 @@
       <c r="A18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlSwaptionVolatilityStructureVolatility(B8,B11,B13,B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="C18" ca="1">_xll.qlSwaptionVolatilityStructureVolatility(C8,C11,C13,C15,C16)</f>
-        <v>#VALUE!</v>
+      <c r="B18" s="6" cm="1">
+        <f t="array" ref="B18">_xll.qlSwaptionVolatilityStructureVolatility(B8,B11,B13,B15)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C18" s="7" cm="1">
+        <f t="array" ref="C18">_xll.qlSwaptionVolatilityStructureVolatility(C8,C11,C13,C15,C16)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="6" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(B8,B12,B14,B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="C19" ca="1">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(C8,C12,C14,C15,C16)</f>
-        <v>#VALUE!</v>
+      <c r="B19" s="6" cm="1">
+        <f t="array" ref="B19">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(B8,B12,B14,B15)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C19" s="7" cm="1">
+        <f t="array" ref="C19">_xll.qlSwaptionVolatilityStructureVolatilityFromTime(C8,C12,C14,C15,C16)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlSwaptionVolatilityStructureBlackVariance(B8,B11,B13,B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="C20" ca="1">_xll.qlSwaptionVolatilityStructureBlackVariance(C8,C11,C13,C15,C16)</f>
-        <v>#VALUE!</v>
+      <c r="B20" s="7" cm="1">
+        <f t="array" ref="B20">_xll.qlSwaptionVolatilityStructureBlackVariance(B8,B11,B13,B15)</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="C20" s="10" cm="1">
+        <f t="array" ref="C20">_xll.qlSwaptionVolatilityStructureBlackVariance(C8,C11,C13,C15,C16)</f>
+        <v>6.3999999999999997E-5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(B8,B12,B14,B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="C21" ca="1">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(C8,C12,C14,C15)</f>
-        <v>#VALUE!</v>
+      <c r="B21" s="7" cm="1">
+        <f t="array" ref="B21">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(B8,B12,B14,B15)</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="C21" s="10" cm="1">
+        <f t="array" ref="C21">_xll.qlSwaptionVolatilityStructureBlackVarianceFromTime(C8,C12,C14,C15)</f>
+        <v>6.3999999999999997E-5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlSwaptionVolatilityStructureShift(B8,B11,B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="12" t="e" cm="1">
-        <f t="array" aca="1" ref="C22" ca="1">FIND("RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities",_xll.qlSwaptionVolatilityStructureShift(C8,C11,C13,C16))</f>
-        <v>#VALUE!</v>
+      <c r="B22" s="7" cm="1">
+        <f t="array" ref="B22">_xll.qlSwaptionVolatilityStructureShift(B8,B11,B13)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="12" cm="1">
+        <f t="array" ref="C22">FIND("RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities",_xll.qlSwaptionVolatilityStructureShift(C8,C11,C13,C16))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlSwaptionVolatilityStructureShiftFromTime(B8,B12,B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="12" t="e" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">FIND("RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities", _xll.qlSwaptionVolatilityStructureShiftFromTime(C8,C12,C14,C16))</f>
-        <v>#VALUE!</v>
+      <c r="B23" s="7" cm="1">
+        <f t="array" ref="B23">_xll.qlSwaptionVolatilityStructureShiftFromTime(B8,B12,B14)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="12" cm="1">
+        <f t="array" ref="C23">FIND("RuntimeError: RuntimeError: shift parameter only makes sense for lognormal volatilities", _xll.qlSwaptionVolatilityStructureShiftFromTime(C8,C12,C14,C16))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlSwaptionVolatilityStructureSmileSection(B8,B11,B13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="C24" ca="1">_xll.qlSwaptionVolatilityStructureSmileSection(C8,C11,C13,C16)</f>
-        <v>#VALUE!</v>
+      <c r="B24" s="3" t="str" cm="1">
+        <f t="array" ref="B24">_xll.qlSwaptionVolatilityStructureSmileSection(B8,B11,B13)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R24C2SmileSection,A</v>
+      </c>
+      <c r="C24" s="3" t="str" cm="1">
+        <f t="array" ref="C24">_xll.qlSwaptionVolatilityStructureSmileSection(C8,C11,C13,C16)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R24C3SmileSection,A</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(B8,B12,B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C25" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="C25" ca="1">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(C8,C12,C14,C16)</f>
-        <v>#VALUE!</v>
+      <c r="B25" s="3" t="str" cm="1">
+        <f t="array" ref="B25">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(B8,B12,B14)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R25C2SmileSection,A</v>
+      </c>
+      <c r="C25" s="3" t="str" cm="1">
+        <f t="array" ref="C25">_xll.qlSwaptionVolatilityStructureSmileSectionFromTime(C8,C12,C14,C16)</f>
+        <v>欣[test_volatilities.xlsx]qlConstantSwaptionVolatility!R25C3SmileSection,A</v>
       </c>
     </row>
   </sheetData>
@@ -1414,7 +1596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8370ED96-400B-4A31-9620-487FCF434FF2}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1471,9 +1653,9 @@
       <c r="D3" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E3" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D3,"Following")</f>
-        <v>#VALUE!</v>
+      <c r="E3" s="1" cm="1">
+        <f t="array" ref="E3">_xll.qlCalendarAdvance2("Target",$B$1,D3,"Following")</f>
+        <v>46539</v>
       </c>
       <c r="F3" s="11">
         <v>8.0000000000000002E-3</v>
@@ -1492,9 +1674,9 @@
       <c r="D4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E4" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D4,"Following")</f>
-        <v>#VALUE!</v>
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xll.qlCalendarAdvance2("Target",$B$1,D4,"Following")</f>
+        <v>46905</v>
       </c>
       <c r="F4" s="11">
         <v>8.0000000000000002E-3</v>
@@ -1513,16 +1695,16 @@
       <c r="A5" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlSwaptionVolatilityMatrix(B1,E3:E7,F2:I2,F3:I7,B2,,"Normal")</f>
-        <v>#VALUE!</v>
+      <c r="B5" s="3" t="str" cm="1">
+        <f t="array" ref="B5">_xll.qlSwaptionVolatilityMatrix(B1,E3:E7,F2:I2,F3:I7,B2,,"Normal")</f>
+        <v>欣[test_volatilities.xlsx]qlSwaptionVolatilityMatrix!R5C2SwaptionVolatilityStructureHandle,A</v>
       </c>
       <c r="D5" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E5" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D5,"Following")</f>
-        <v>#VALUE!</v>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xll.qlCalendarAdvance2("Target",$B$1,D5,"Following")</f>
+        <v>47270</v>
       </c>
       <c r="F5" s="11">
         <v>8.0000000000000002E-3</v>
@@ -1541,9 +1723,9 @@
       <c r="D6" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E6" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D6,"Following")</f>
-        <v>#VALUE!</v>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xll.qlCalendarAdvance2("Target",$B$1,D6,"Following")</f>
+        <v>47637</v>
       </c>
       <c r="F6" s="11">
         <v>8.0000000000000002E-3</v>
@@ -1562,16 +1744,16 @@
       <c r="A7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="11" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlSwaptionVolatilityStructureVolatility(B5,E4+180,"3y",0)</f>
-        <v>#VALUE!</v>
+      <c r="B7" s="11" cm="1">
+        <f t="array" ref="B7">_xll.qlSwaptionVolatilityStructureVolatility(B5,E4+180,"3y",0)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E7" ca="1">_xll.qlCalendarAdvance2("Target",$B$1,D7,"Following")</f>
-        <v>#VALUE!</v>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xll.qlCalendarAdvance2("Target",$B$1,D7,"Following")</f>
+        <v>48001</v>
       </c>
       <c r="F7" s="11">
         <v>8.0000000000000002E-3</v>

--- a/tests/workbooktests/workbooks/test_volatilities.xlsx
+++ b/tests/workbooktests/workbooks/test_volatilities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E732A2BE-9EB0-4965-AB58-34488662C1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6784C484-52CA-4C8A-979A-2BD58C55CD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{03D12B07-F690-4065-A8E3-371E349FECFA}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{03D12B07-F690-4065-A8E3-371E349FECFA}"/>
   </bookViews>
   <sheets>
     <sheet name="qlBlackConstantVol" sheetId="1" r:id="rId1"/>
@@ -1654,7 +1654,7 @@
         <v>65</v>
       </c>
       <c r="E3" s="1" cm="1">
-        <f t="array" ref="E3">_xll.qlCalendarAdvance2("Target",$B$1,D3,"Following")</f>
+        <f t="array" ref="E3">_xll.qlCalendarAdvance("Target",$B$1,D3,"Following")</f>
         <v>46539</v>
       </c>
       <c r="F3" s="11">
@@ -1675,7 +1675,7 @@
         <v>70</v>
       </c>
       <c r="E4" s="1" cm="1">
-        <f t="array" ref="E4">_xll.qlCalendarAdvance2("Target",$B$1,D4,"Following")</f>
+        <f t="array" ref="E4">_xll.qlCalendarAdvance("Target",$B$1,D4,"Following")</f>
         <v>46905</v>
       </c>
       <c r="F4" s="11">
@@ -1703,7 +1703,7 @@
         <v>66</v>
       </c>
       <c r="E5" s="1" cm="1">
-        <f t="array" ref="E5">_xll.qlCalendarAdvance2("Target",$B$1,D5,"Following")</f>
+        <f t="array" ref="E5">_xll.qlCalendarAdvance("Target",$B$1,D5,"Following")</f>
         <v>47270</v>
       </c>
       <c r="F5" s="11">
@@ -1724,7 +1724,7 @@
         <v>67</v>
       </c>
       <c r="E6" s="1" cm="1">
-        <f t="array" ref="E6">_xll.qlCalendarAdvance2("Target",$B$1,D6,"Following")</f>
+        <f t="array" ref="E6">_xll.qlCalendarAdvance("Target",$B$1,D6,"Following")</f>
         <v>47637</v>
       </c>
       <c r="F6" s="11">
@@ -1752,7 +1752,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="1" cm="1">
-        <f t="array" ref="E7">_xll.qlCalendarAdvance2("Target",$B$1,D7,"Following")</f>
+        <f t="array" ref="E7">_xll.qlCalendarAdvance("Target",$B$1,D7,"Following")</f>
         <v>48001</v>
       </c>
       <c r="F7" s="11">
